--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichaelBurke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7C40C-1D33-4599-841E-11C9987AA209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA721CB2-EA89-4845-899D-05CC18CEB147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0" iterate="1"/>
 </workbook>
 </file>
 

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichaelBurke\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA721CB2-EA89-4845-899D-05CC18CEB147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
